--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>8.23</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>6.96</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>6.81</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>6.68</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>6.61</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>6.44</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>6.09</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>5.89</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>5.71</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>5.69</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>5.6</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>5.57</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>5.46</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>5.31</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>5.19</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>5.15</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>5.11</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>5.07</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>5</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>4.99</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>4.96</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>4.91</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>4.83</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>4.8</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>4.73</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>4.69</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>4.64</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>4.4</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>4.39</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>4.26</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>4.26</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>4.24</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>4.18</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>4.17</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>4.12</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>4.1</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>4.08</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -877,9 +761,6 @@
       <c r="B39">
         <v>3.93</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,9 +771,6 @@
       <c r="B40">
         <v>3.75</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -903,9 +781,6 @@
       <c r="B41">
         <v>3.64</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -916,9 +791,6 @@
       <c r="B42">
         <v>3.59</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -929,9 +801,6 @@
       <c r="B43">
         <v>3.52</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -942,9 +811,6 @@
       <c r="B44">
         <v>3.4</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,9 +821,6 @@
       <c r="B45">
         <v>3.37</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -968,9 +831,6 @@
       <c r="B46">
         <v>3.26</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -981,9 +841,6 @@
       <c r="B47">
         <v>3.24</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -994,9 +851,6 @@
       <c r="B48">
         <v>3.02</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1007,9 +861,6 @@
       <c r="B49">
         <v>3</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1020,9 +871,6 @@
       <c r="B50">
         <v>2.06</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1033,9 +881,6 @@
       <c r="B51">
         <v>1.83</v>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1046,9 +891,6 @@
       <c r="B52">
         <v>1.75</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1058,9 +900,6 @@
       </c>
       <c r="B53">
         <v>1.68</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>8.23</v>
       </c>
+      <c r="C2">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="D2">
+        <v>-1.16</v>
+      </c>
+      <c r="E2">
+        <v>-12.35356762513312</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>6.96</v>
       </c>
+      <c r="C3">
+        <v>7.06</v>
+      </c>
+      <c r="D3">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="E3">
+        <v>-1.416430594900842</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>6.81</v>
       </c>
+      <c r="C4">
+        <v>6.79</v>
+      </c>
+      <c r="D4">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E4">
+        <v>0.2945508100147265</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>6.68</v>
       </c>
+      <c r="C5">
+        <v>8.84</v>
+      </c>
+      <c r="D5">
+        <v>-2.16</v>
+      </c>
+      <c r="E5">
+        <v>-24.4343891402715</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>6.61</v>
       </c>
+      <c r="C6">
+        <v>7.02</v>
+      </c>
+      <c r="D6">
+        <v>-0.4099999999999993</v>
+      </c>
+      <c r="E6">
+        <v>-5.840455840455827</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>6.44</v>
       </c>
+      <c r="C7">
+        <v>7.18</v>
+      </c>
+      <c r="D7">
+        <v>-0.7399999999999993</v>
+      </c>
+      <c r="E7">
+        <v>-10.30640668523676</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>6.09</v>
       </c>
+      <c r="C8">
+        <v>6.26</v>
+      </c>
+      <c r="D8">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="E8">
+        <v>-2.715654952076674</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>5.89</v>
       </c>
+      <c r="C9">
+        <v>6.09</v>
+      </c>
+      <c r="D9">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="E9">
+        <v>-3.284072249589498</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>5.71</v>
       </c>
+      <c r="C10">
+        <v>6.25</v>
+      </c>
+      <c r="D10">
+        <v>-0.54</v>
+      </c>
+      <c r="E10">
+        <v>-8.640000000000004</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>5.69</v>
       </c>
+      <c r="C11">
+        <v>6.17</v>
+      </c>
+      <c r="D11">
+        <v>-0.4799999999999995</v>
+      </c>
+      <c r="E11">
+        <v>-7.779578606158822</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>5.6</v>
       </c>
+      <c r="C12">
+        <v>5.55</v>
+      </c>
+      <c r="D12">
+        <v>0.04999999999999982</v>
+      </c>
+      <c r="E12">
+        <v>0.9009009009008917</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +600,15 @@
       <c r="B13">
         <v>5.57</v>
       </c>
+      <c r="C13">
+        <v>6.4</v>
+      </c>
+      <c r="D13">
+        <v>-0.8300000000000001</v>
+      </c>
+      <c r="E13">
+        <v>-12.96875</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +619,15 @@
       <c r="B14">
         <v>5.46</v>
       </c>
+      <c r="C14">
+        <v>5.78</v>
+      </c>
+      <c r="D14">
+        <v>-0.3200000000000003</v>
+      </c>
+      <c r="E14">
+        <v>-5.536332179930803</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,6 +638,15 @@
       <c r="B15">
         <v>5.31</v>
       </c>
+      <c r="C15">
+        <v>5.72</v>
+      </c>
+      <c r="D15">
+        <v>-0.4100000000000001</v>
+      </c>
+      <c r="E15">
+        <v>-7.167832167832167</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -531,6 +657,15 @@
       <c r="B16">
         <v>5.19</v>
       </c>
+      <c r="C16">
+        <v>5.61</v>
+      </c>
+      <c r="D16">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="E16">
+        <v>-7.486631016042777</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -541,6 +676,15 @@
       <c r="B17">
         <v>5.15</v>
       </c>
+      <c r="C17">
+        <v>5.57</v>
+      </c>
+      <c r="D17">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="E17">
+        <v>-7.540394973070019</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -551,6 +695,15 @@
       <c r="B18">
         <v>5.11</v>
       </c>
+      <c r="C18">
+        <v>5.44</v>
+      </c>
+      <c r="D18">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="E18">
+        <v>-6.066176470588236</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -561,6 +714,15 @@
       <c r="B19">
         <v>5.07</v>
       </c>
+      <c r="C19">
+        <v>5.45</v>
+      </c>
+      <c r="D19">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="E19">
+        <v>-6.972477064220184</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -571,6 +733,15 @@
       <c r="B20">
         <v>5</v>
       </c>
+      <c r="C20">
+        <v>5.6</v>
+      </c>
+      <c r="D20">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="E20">
+        <v>-10.71428571428571</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -581,6 +752,15 @@
       <c r="B21">
         <v>4.99</v>
       </c>
+      <c r="C21">
+        <v>5.27</v>
+      </c>
+      <c r="D21">
+        <v>-0.2799999999999994</v>
+      </c>
+      <c r="E21">
+        <v>-5.313092979127121</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -591,6 +771,15 @@
       <c r="B22">
         <v>4.96</v>
       </c>
+      <c r="C22">
+        <v>5.35</v>
+      </c>
+      <c r="D22">
+        <v>-0.3899999999999997</v>
+      </c>
+      <c r="E22">
+        <v>-7.289719626168223</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -601,6 +790,15 @@
       <c r="B23">
         <v>4.91</v>
       </c>
+      <c r="C23">
+        <v>5.48</v>
+      </c>
+      <c r="D23">
+        <v>-0.5700000000000003</v>
+      </c>
+      <c r="E23">
+        <v>-10.40145985401461</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -611,6 +809,15 @@
       <c r="B24">
         <v>4.83</v>
       </c>
+      <c r="C24">
+        <v>5.24</v>
+      </c>
+      <c r="D24">
+        <v>-0.4100000000000001</v>
+      </c>
+      <c r="E24">
+        <v>-7.82442748091603</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -621,6 +828,15 @@
       <c r="B25">
         <v>4.8</v>
       </c>
+      <c r="C25">
+        <v>5.11</v>
+      </c>
+      <c r="D25">
+        <v>-0.3100000000000005</v>
+      </c>
+      <c r="E25">
+        <v>-6.06653620352251</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -631,6 +847,15 @@
       <c r="B26">
         <v>4.73</v>
       </c>
+      <c r="C26">
+        <v>4.95</v>
+      </c>
+      <c r="D26">
+        <v>-0.2199999999999998</v>
+      </c>
+      <c r="E26">
+        <v>-4.444444444444439</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -641,6 +866,15 @@
       <c r="B27">
         <v>4.69</v>
       </c>
+      <c r="C27">
+        <v>5.34</v>
+      </c>
+      <c r="D27">
+        <v>-0.6499999999999995</v>
+      </c>
+      <c r="E27">
+        <v>-12.17228464419474</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -651,6 +885,15 @@
       <c r="B28">
         <v>4.64</v>
       </c>
+      <c r="C28">
+        <v>5.09</v>
+      </c>
+      <c r="D28">
+        <v>-0.4500000000000002</v>
+      </c>
+      <c r="E28">
+        <v>-8.840864440078589</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -661,6 +904,15 @@
       <c r="B29">
         <v>4.4</v>
       </c>
+      <c r="C29">
+        <v>4.71</v>
+      </c>
+      <c r="D29">
+        <v>-0.3099999999999996</v>
+      </c>
+      <c r="E29">
+        <v>-6.581740976645422</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -671,6 +923,15 @@
       <c r="B30">
         <v>4.39</v>
       </c>
+      <c r="C30">
+        <v>4.56</v>
+      </c>
+      <c r="D30">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="E30">
+        <v>-3.728070175438591</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -681,6 +942,15 @@
       <c r="B31">
         <v>4.26</v>
       </c>
+      <c r="C31">
+        <v>4.59</v>
+      </c>
+      <c r="D31">
+        <v>-0.3300000000000001</v>
+      </c>
+      <c r="E31">
+        <v>-7.189542483660127</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -691,6 +961,15 @@
       <c r="B32">
         <v>4.26</v>
       </c>
+      <c r="C32">
+        <v>4.56</v>
+      </c>
+      <c r="D32">
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="E32">
+        <v>-6.578947368421051</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -701,6 +980,15 @@
       <c r="B33">
         <v>4.24</v>
       </c>
+      <c r="C33">
+        <v>5.05</v>
+      </c>
+      <c r="D33">
+        <v>-0.8099999999999996</v>
+      </c>
+      <c r="E33">
+        <v>-16.03960396039603</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -711,6 +999,15 @@
       <c r="B34">
         <v>4.18</v>
       </c>
+      <c r="C34">
+        <v>4.47</v>
+      </c>
+      <c r="D34">
+        <v>-0.29</v>
+      </c>
+      <c r="E34">
+        <v>-6.487695749440714</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -721,6 +1018,15 @@
       <c r="B35">
         <v>4.17</v>
       </c>
+      <c r="C35">
+        <v>4.6</v>
+      </c>
+      <c r="D35">
+        <v>-0.4299999999999997</v>
+      </c>
+      <c r="E35">
+        <v>-9.347826086956513</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -731,6 +1037,15 @@
       <c r="B36">
         <v>4.12</v>
       </c>
+      <c r="C36">
+        <v>4.54</v>
+      </c>
+      <c r="D36">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="E36">
+        <v>-9.251101321585898</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -741,6 +1056,15 @@
       <c r="B37">
         <v>4.1</v>
       </c>
+      <c r="C37">
+        <v>4.64</v>
+      </c>
+      <c r="D37">
+        <v>-0.54</v>
+      </c>
+      <c r="E37">
+        <v>-11.63793103448276</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -751,155 +1075,309 @@
       <c r="B38">
         <v>4.08</v>
       </c>
+      <c r="C38">
+        <v>4.37</v>
+      </c>
+      <c r="D38">
+        <v>-0.29</v>
+      </c>
+      <c r="E38">
+        <v>-6.636155606407323</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B39">
-        <v>3.93</v>
+        <v>4.08</v>
+      </c>
+      <c r="C39">
+        <v>4.46</v>
+      </c>
+      <c r="D39">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="E39">
+        <v>-8.520179372197312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="B40">
-        <v>3.75</v>
+        <v>3.93</v>
+      </c>
+      <c r="C40">
+        <v>4.16</v>
+      </c>
+      <c r="D40">
+        <v>-0.23</v>
+      </c>
+      <c r="E40">
+        <v>-5.528846153846157</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="B41">
-        <v>3.64</v>
+        <v>3.75</v>
+      </c>
+      <c r="C41">
+        <v>4.03</v>
+      </c>
+      <c r="D41">
+        <v>-0.2800000000000002</v>
+      </c>
+      <c r="E41">
+        <v>-6.947890818858571</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="B42">
-        <v>3.59</v>
+        <v>3.64</v>
+      </c>
+      <c r="C42">
+        <v>3.94</v>
+      </c>
+      <c r="D42">
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="E42">
+        <v>-7.614213197969544</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="B43">
-        <v>3.52</v>
+        <v>3.59</v>
+      </c>
+      <c r="C43">
+        <v>3.87</v>
+      </c>
+      <c r="D43">
+        <v>-0.2800000000000002</v>
+      </c>
+      <c r="E43">
+        <v>-7.235142118863058</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="B44">
-        <v>3.4</v>
+        <v>3.52</v>
+      </c>
+      <c r="C44">
+        <v>3.75</v>
+      </c>
+      <c r="D44">
+        <v>-0.23</v>
+      </c>
+      <c r="E44">
+        <v>-6.133333333333335</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="B45">
-        <v>3.37</v>
+        <v>3.4</v>
+      </c>
+      <c r="C45">
+        <v>3.8</v>
+      </c>
+      <c r="D45">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="E45">
+        <v>-10.52631578947368</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="B46">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="B47">
-        <v>3.24</v>
+        <v>3.26</v>
+      </c>
+      <c r="C47">
+        <v>3.54</v>
+      </c>
+      <c r="D47">
+        <v>-0.2800000000000002</v>
+      </c>
+      <c r="E47">
+        <v>-7.909604519774016</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>La Reina</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="B48">
-        <v>3.02</v>
+        <v>3.24</v>
+      </c>
+      <c r="C48">
+        <v>3.52</v>
+      </c>
+      <c r="D48">
+        <v>-0.2799999999999998</v>
+      </c>
+      <c r="E48">
+        <v>-7.954545454545448</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>La Reina</t>
         </is>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>3.02</v>
+      </c>
+      <c r="C49">
+        <v>3.18</v>
+      </c>
+      <c r="D49">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="E49">
+        <v>-5.031446540880502</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="B50">
-        <v>2.06</v>
+        <v>3</v>
+      </c>
+      <c r="C50">
+        <v>3.22</v>
+      </c>
+      <c r="D50">
+        <v>-0.2200000000000002</v>
+      </c>
+      <c r="E50">
+        <v>-6.832298136645965</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="B51">
-        <v>1.83</v>
+        <v>2.06</v>
+      </c>
+      <c r="C51">
+        <v>2.21</v>
+      </c>
+      <c r="D51">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="E51">
+        <v>-6.78733031674208</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.75</v>
+        <v>1.83</v>
+      </c>
+      <c r="C52">
+        <v>1.9</v>
+      </c>
+      <c r="D52">
+        <v>-0.06999999999999984</v>
+      </c>
+      <c r="E52">
+        <v>-3.684210526315779</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1.75</v>
+      </c>
+      <c r="C53">
+        <v>1.76</v>
+      </c>
+      <c r="D53">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="E53">
+        <v>-0.5681818181818232</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Vitacura</t>
         </is>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>1.68</v>
+      </c>
+      <c r="C54">
+        <v>1.8</v>
+      </c>
+      <c r="D54">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="E54">
+        <v>-6.666666666666677</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_metropolitana.xlsx
@@ -1387,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1396,530 +1396,369 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>6.68</v>
+          <t>San Joaquín</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>4.8</v>
+          <t>San Miguel</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>5.57</v>
+          <t>San Ramón</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>4.26</v>
+          <t>Independencia</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5.31</v>
+          <t>La Cisterna</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.1</v>
+          <t>Peñalolén</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>5</v>
+          <t>Providencia</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>6.09</v>
+          <t>La Reina</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>4.64</v>
+          <t>Calera de Tango</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>5.89</v>
+          <t>Colina</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>4.91</v>
+          <t>Santiago</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>3.24</v>
+          <t>Lampa</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>5.71</v>
+          <t>Pirque</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>6.81</v>
+          <t>Puente Alto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>4.26</v>
+          <t>Huechuraba</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>3.75</v>
+          <t>San Bernardo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>4.99</v>
+          <t>Curacaví</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>5.11</v>
+          <t>María Pinto</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>3.02</v>
+          <t>Cerrillos</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>3.64</v>
+          <t>Cerro Navia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>1.83</v>
+          <t>Vitacura</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>3</v>
+          <t>Conchalí</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>4.69</v>
+          <t>El Bosque</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>5.19</v>
+          <t>Estación Central</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>3.59</v>
+          <t>La Florida</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>3.52</v>
+          <t>La Granja</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>6.44</v>
+          <t>La Pintana</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>6.96</v>
+          <t>Las Condes</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>2.06</v>
+          <t>Lo Barnechea</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>4.12</v>
+          <t>Lo Espejo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>6.61</v>
+          <t>Lo Prado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>4.96</v>
+          <t>Macul</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>4.39</v>
+          <t>Maipú</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>4.83</v>
+          <t>Ñuñoa</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>5.6</v>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>1.75</v>
+          <t>Pudahuel</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>4.08</v>
+          <t>Quilicura</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>3.93</v>
+          <t>Quinta Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>3.4</v>
+          <t>Recoleta</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>5.15</v>
+          <t>Renca</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>5.69</v>
+          <t>El Monte</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>4.17</v>
+          <t>Padre Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>4.18</v>
+          <t>Peñaflor</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>4.73</v>
+          <t>Talagante</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>4.4</v>
+          <t>Paine</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>3.26</v>
+          <t>Isla de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>8.23</v>
+          <t>Buin</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>5.07</v>
+          <t>San José de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>4.24</v>
+          <t>Tiltil</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>5.46</v>
+          <t>Melipilla</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tiltil</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>3.37</v>
+          <t>San Pedro</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>1.68</v>
+          <t>Alhué</t>
+        </is>
       </c>
     </row>
   </sheetData>
